--- a/hira_material_automation/output/monthly/202601_202609__arthroscopy_cannula__041001__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202609__arthroscopy_cannula__041001__normalized.xlsx
@@ -785,7 +785,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-04T22:54:04</t>
+          <t>2026-09-14T23:45:38</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>b50e8f0288deeda2c86acafb8d5b4a5fed13882a2b9e5991dc42315297b53731</t>
+          <t>6b1d1bbca1ffcc8a8a9286fe52c9c56c101bc7faca0c0061cef0a4922f4fc3d1</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202609__arthroscopy_cannula__041001__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202609__arthroscopy_cannula__041001__normalized.xlsx
@@ -785,7 +785,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-14T23:45:38</t>
+          <t>2026-09-24T23:49:01</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6b1d1bbca1ffcc8a8a9286fe52c9c56c101bc7faca0c0061cef0a4922f4fc3d1</t>
+          <t>da4c9279b983541e40efad79da88ff55cf1680da3d32062d4f087a1a5737a1d8</t>
         </is>
       </c>
     </row>
